--- a/Четверг.xlsx
+++ b/Четверг.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pinchukna\Desktop\Посещаемость\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pinchukna\Documents\Folder\Generator_rep_attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" refMode="R1C1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>№</t>
   </si>
@@ -87,13 +87,10 @@
     <t>Кинетов Жан Бахытович</t>
   </si>
   <si>
-    <t>Абдрахман Хасен Алпамысович</t>
-  </si>
-  <si>
     <t>С 8:15</t>
   </si>
   <si>
-    <t>С 18:00-22:30</t>
+    <t>Абдрахманов Хасен Алпамысович</t>
   </si>
 </sst>
 </file>
@@ -814,7 +811,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="5"/>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -869,26 +866,23 @@
       <c r="C8" s="5">
         <v>9433307</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="J8" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="K8" s="5"/>
-      <c r="L8" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16">
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="7">
         <v>9433309</v>
